--- a/组合实盘追踪/20260519_银河.xlsx
+++ b/组合实盘追踪/20260519_银河.xlsx
@@ -532,13 +532,13 @@
         <v>1000ETF</v>
       </c>
       <c r="C2" s="1">
-        <v>702.4</v>
+        <v>708.4</v>
       </c>
       <c r="D2" s="1">
-        <v>1.8</v>
+        <v>7.8</v>
       </c>
       <c r="E2" s="2">
-        <v>0.0026</v>
+        <v>0.0111</v>
       </c>
       <c r="F2" t="str">
         <v/>
@@ -553,25 +553,25 @@
         <v/>
       </c>
       <c r="J2" s="1">
-        <v>-8.7</v>
+        <v>-2.7</v>
       </c>
       <c r="K2" s="2">
-        <v>-0.0122</v>
+        <v>-0.0038</v>
       </c>
       <c r="L2" s="1">
-        <v>-8.7</v>
+        <v>-2.7</v>
       </c>
       <c r="M2" s="2">
-        <v>-0.0122</v>
+        <v>-0.0038</v>
       </c>
       <c r="N2" s="1">
-        <v>0.8</v>
+        <v>7.2</v>
       </c>
       <c r="O2" s="1">
-        <v>-9.5</v>
+        <v>-2.7</v>
       </c>
       <c r="P2" s="1">
-        <v>-9.5</v>
+        <v>-2.7</v>
       </c>
       <c r="Q2" s="2">
         <v>0.0238</v>
@@ -583,28 +583,28 @@
         <v>7</v>
       </c>
       <c r="T2" s="2">
-        <v>0.0026</v>
+        <v>0.0111</v>
       </c>
       <c r="U2" s="5">
-        <v>3.512</v>
+        <v>3.542</v>
       </c>
       <c r="V2" s="5">
         <v>3.556</v>
       </c>
       <c r="W2" s="2">
-        <v>0.0125</v>
+        <v>0.004</v>
       </c>
       <c r="X2" s="2">
-        <v>0.0547</v>
+        <v>0.0637</v>
       </c>
       <c r="Y2" s="2">
-        <v>0.0691</v>
+        <v>0.0783</v>
       </c>
       <c r="Z2" s="2">
-        <v>0.1781</v>
+        <v>0.1882</v>
       </c>
       <c r="AA2" s="2">
-        <v>0.462</v>
+        <v>0.4745</v>
       </c>
     </row>
     <row r="3">
@@ -615,13 +615,13 @@
         <v>豆粕ETF</v>
       </c>
       <c r="C3" s="1">
-        <v>849.6</v>
+        <v>848.8</v>
       </c>
       <c r="D3" s="1">
-        <v>12.8</v>
+        <v>12</v>
       </c>
       <c r="E3" s="2">
-        <v>0.0153</v>
+        <v>0.0143</v>
       </c>
       <c r="F3" t="str">
         <v/>
@@ -636,28 +636,28 @@
         <v/>
       </c>
       <c r="J3" s="1">
-        <v>-13.3</v>
+        <v>-14.1</v>
       </c>
       <c r="K3" s="2">
-        <v>-0.0154</v>
+        <v>-0.0163</v>
       </c>
       <c r="L3" s="1">
-        <v>-13.3</v>
+        <v>-14.1</v>
       </c>
       <c r="M3" s="2">
-        <v>-0.0154</v>
+        <v>-0.0163</v>
       </c>
       <c r="N3" s="1">
-        <v>5.2</v>
+        <v>4.8</v>
       </c>
       <c r="O3" s="1">
-        <v>-13.7</v>
+        <v>-14.1</v>
       </c>
       <c r="P3" s="1">
-        <v>-13.7</v>
+        <v>-14.1</v>
       </c>
       <c r="Q3" s="2">
-        <v>0.0288</v>
+        <v>0.0285</v>
       </c>
       <c r="R3" s="3">
         <v>400</v>
@@ -666,28 +666,28 @@
         <v>7</v>
       </c>
       <c r="T3" s="2">
-        <v>0.0153</v>
+        <v>0.0143</v>
       </c>
       <c r="U3" s="5">
-        <v>2.124</v>
+        <v>2.122</v>
       </c>
       <c r="V3" s="5">
         <v>2.157</v>
       </c>
       <c r="W3" s="2">
-        <v>0.0155</v>
+        <v>0.0165</v>
       </c>
       <c r="X3" s="2">
-        <v>0.0143</v>
+        <v>0.0133</v>
       </c>
       <c r="Y3" s="2">
-        <v>0.062</v>
+        <v>0.061</v>
       </c>
       <c r="Z3" s="2">
-        <v>0.0536</v>
+        <v>0.0526</v>
       </c>
       <c r="AA3" s="2">
-        <v>0.115</v>
+        <v>0.1139</v>
       </c>
     </row>
     <row r="4">
@@ -698,13 +698,13 @@
         <v>港股科技</v>
       </c>
       <c r="C4" s="1">
-        <v>704</v>
+        <v>702.9</v>
       </c>
       <c r="D4" s="1">
-        <v>3.3</v>
+        <v>2.2</v>
       </c>
       <c r="E4" s="2">
-        <v>0.0047</v>
+        <v>0.0031</v>
       </c>
       <c r="F4" t="str">
         <v/>
@@ -719,28 +719,28 @@
         <v/>
       </c>
       <c r="J4" s="1">
-        <v>-33.1</v>
+        <v>-34.2</v>
       </c>
       <c r="K4" s="2">
-        <v>-0.0449</v>
+        <v>-0.0464</v>
       </c>
       <c r="L4" s="1">
-        <v>-33.1</v>
+        <v>-34.2</v>
       </c>
       <c r="M4" s="2">
-        <v>-0.0449</v>
+        <v>-0.0464</v>
       </c>
       <c r="N4" s="1">
-        <v>-15.4</v>
+        <v>-17.6</v>
       </c>
       <c r="O4" s="1">
-        <v>-30.9</v>
+        <v>-34.2</v>
       </c>
       <c r="P4" s="1">
-        <v>-30.9</v>
+        <v>-34.2</v>
       </c>
       <c r="Q4" s="2">
-        <v>0.0239</v>
+        <v>0.0236</v>
       </c>
       <c r="R4" s="3">
         <v>1100</v>
@@ -749,28 +749,28 @@
         <v>7</v>
       </c>
       <c r="T4" s="2">
-        <v>0.0047</v>
+        <v>0.0031</v>
       </c>
       <c r="U4" s="5">
-        <v>0.64</v>
+        <v>0.639</v>
       </c>
       <c r="V4" s="5">
         <v>0.67</v>
       </c>
       <c r="W4" s="2">
-        <v>0.0469</v>
+        <v>0.0485</v>
       </c>
       <c r="X4" s="2">
-        <v>-0.0333</v>
+        <v>-0.0348</v>
       </c>
       <c r="Y4" s="2">
-        <v>-0.1148</v>
+        <v>-0.1161</v>
       </c>
       <c r="Z4" s="2">
-        <v>-0.1784</v>
+        <v>-0.1797</v>
       </c>
       <c r="AA4" s="2">
-        <v>-0.1245</v>
+        <v>-0.1259</v>
       </c>
     </row>
     <row r="5">
@@ -781,13 +781,13 @@
         <v>300ETF</v>
       </c>
       <c r="C5" s="1">
-        <v>966.8</v>
+        <v>973.8</v>
       </c>
       <c r="D5" s="1">
-        <v>-3.6</v>
+        <v>3.4</v>
       </c>
       <c r="E5" s="2">
-        <v>-0.0037</v>
+        <v>0.0035</v>
       </c>
       <c r="F5" t="str">
         <v/>
@@ -802,28 +802,28 @@
         <v/>
       </c>
       <c r="J5" s="1">
-        <v>-24.5</v>
+        <v>-17.5</v>
       </c>
       <c r="K5" s="2">
-        <v>-0.0247</v>
+        <v>-0.0177</v>
       </c>
       <c r="L5" s="1">
-        <v>-24.5</v>
+        <v>-17.5</v>
       </c>
       <c r="M5" s="2">
-        <v>-0.0247</v>
+        <v>-0.0177</v>
       </c>
       <c r="N5" s="1">
-        <v>-12.6</v>
+        <v>-5.6</v>
       </c>
       <c r="O5" s="1">
-        <v>-23.9</v>
+        <v>-17.5</v>
       </c>
       <c r="P5" s="1">
-        <v>-23.9</v>
+        <v>-17.5</v>
       </c>
       <c r="Q5" s="2">
-        <v>0.0328</v>
+        <v>0.0327</v>
       </c>
       <c r="R5" s="3">
         <v>200</v>
@@ -832,28 +832,28 @@
         <v>7</v>
       </c>
       <c r="T5" s="2">
-        <v>-0.0037</v>
+        <v>0.0035</v>
       </c>
       <c r="U5" s="5">
-        <v>4.834</v>
+        <v>4.869</v>
       </c>
       <c r="V5" s="5">
         <v>4.957</v>
       </c>
       <c r="W5" s="2">
-        <v>0.0254</v>
+        <v>0.0181</v>
       </c>
       <c r="X5" s="2">
-        <v>0.02</v>
+        <v>0.0274</v>
       </c>
       <c r="Y5" s="2">
-        <v>0.0348</v>
+        <v>0.0423</v>
       </c>
       <c r="Z5" s="2">
-        <v>0.0591</v>
+        <v>0.0667</v>
       </c>
       <c r="AA5" s="2">
-        <v>0.2714</v>
+        <v>0.2806</v>
       </c>
     </row>
     <row r="6">
@@ -864,13 +864,13 @@
         <v>黄金ETF</v>
       </c>
       <c r="C6" s="1">
-        <v>955.4</v>
+        <v>951.5</v>
       </c>
       <c r="D6" s="1">
-        <v>4.1</v>
+        <v>0.2</v>
       </c>
       <c r="E6" s="2">
-        <v>0.0043</v>
+        <v>0.0002</v>
       </c>
       <c r="F6" t="str">
         <v/>
@@ -885,28 +885,28 @@
         <v/>
       </c>
       <c r="J6" s="1">
-        <v>-18.3</v>
+        <v>-22.2</v>
       </c>
       <c r="K6" s="2">
-        <v>-0.0188</v>
+        <v>-0.0228</v>
       </c>
       <c r="L6" s="1">
-        <v>-18.3</v>
+        <v>-22.2</v>
       </c>
       <c r="M6" s="2">
-        <v>-0.0188</v>
+        <v>-0.0228</v>
       </c>
       <c r="N6" s="1">
-        <v>-8.4</v>
+        <v>-12.3</v>
       </c>
       <c r="O6" s="1">
-        <v>-18.3</v>
+        <v>-22.2</v>
       </c>
       <c r="P6" s="1">
-        <v>-18.3</v>
+        <v>-22.2</v>
       </c>
       <c r="Q6" s="2">
-        <v>0.0324</v>
+        <v>0.032</v>
       </c>
       <c r="R6" s="3">
         <v>100</v>
@@ -915,28 +915,28 @@
         <v>7</v>
       </c>
       <c r="T6" s="2">
-        <v>0.0043</v>
+        <v>0.0002</v>
       </c>
       <c r="U6" s="5">
-        <v>9.554</v>
+        <v>9.515</v>
       </c>
       <c r="V6" s="5">
         <v>9.737</v>
       </c>
       <c r="W6" s="2">
-        <v>0.0192</v>
+        <v>0.0233</v>
       </c>
       <c r="X6" s="2">
-        <v>-0.0474</v>
+        <v>-0.0513</v>
       </c>
       <c r="Y6" s="2">
-        <v>-0.0965</v>
+        <v>-0.1002</v>
       </c>
       <c r="Z6" s="2">
-        <v>0.0886</v>
+        <v>0.0841</v>
       </c>
       <c r="AA6" s="2">
-        <v>0.3312</v>
+        <v>0.3258</v>
       </c>
     </row>
     <row r="7">
@@ -947,13 +947,13 @@
         <v>中欧纯债</v>
       </c>
       <c r="C7" s="1">
-        <v>3018.6</v>
+        <v>3024</v>
       </c>
       <c r="D7" s="1">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="E7" s="2">
-        <v>0</v>
+        <v>0.0018</v>
       </c>
       <c r="F7" t="str">
         <v/>
@@ -968,28 +968,28 @@
         <v/>
       </c>
       <c r="J7" s="1">
-        <v>-0.15</v>
+        <v>5.25</v>
       </c>
       <c r="K7" s="2">
-        <v>0</v>
+        <v>0.0017</v>
       </c>
       <c r="L7" s="1">
-        <v>-0.15</v>
+        <v>5.25</v>
       </c>
       <c r="M7" s="2">
-        <v>0</v>
+        <v>0.0017</v>
       </c>
       <c r="N7" s="1">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="O7" s="1">
-        <v>-0.15</v>
+        <v>5.25</v>
       </c>
       <c r="P7" s="1">
-        <v>-0.15</v>
+        <v>5.25</v>
       </c>
       <c r="Q7" s="2">
-        <v>0.1023</v>
+        <v>0.1016</v>
       </c>
       <c r="R7" s="3">
         <v>2700</v>
@@ -998,10 +998,10 @@
         <v>7</v>
       </c>
       <c r="T7" s="2">
-        <v>0</v>
+        <v>0.0018</v>
       </c>
       <c r="U7" s="5">
-        <v>1.118</v>
+        <v>1.12</v>
       </c>
       <c r="V7" s="5">
         <v>1.118</v>
@@ -1010,16 +1010,16 @@
         <v/>
       </c>
       <c r="X7" s="2">
-        <v>0.0009</v>
+        <v>0.0027</v>
       </c>
       <c r="Y7" s="2">
-        <v>0.0072</v>
+        <v>0.009</v>
       </c>
       <c r="Z7" s="2">
-        <v>0.0099</v>
+        <v>0.0117</v>
       </c>
       <c r="AA7" s="2">
-        <v>0.0207</v>
+        <v>0.0225</v>
       </c>
     </row>
     <row r="8">
@@ -1030,13 +1030,13 @@
         <v>创业板</v>
       </c>
       <c r="C8" s="1">
-        <v>778.4</v>
+        <v>784.4</v>
       </c>
       <c r="D8" s="1">
-        <v>-6.2</v>
+        <v>-0.2</v>
       </c>
       <c r="E8" s="2">
-        <v>-0.0079</v>
+        <v>-0.0003</v>
       </c>
       <c r="F8" t="str">
         <v/>
@@ -1051,25 +1051,25 @@
         <v/>
       </c>
       <c r="J8" s="1">
-        <v>-8.3</v>
+        <v>-2.3</v>
       </c>
       <c r="K8" s="2">
-        <v>-0.0105</v>
+        <v>-0.0029</v>
       </c>
       <c r="L8" s="1">
-        <v>-8.3</v>
+        <v>-2.3</v>
       </c>
       <c r="M8" s="2">
-        <v>-0.0105</v>
+        <v>-0.0029</v>
       </c>
       <c r="N8" s="1">
-        <v>-6.8</v>
+        <v>-0.4</v>
       </c>
       <c r="O8" s="1">
-        <v>-8.7</v>
+        <v>-2.3</v>
       </c>
       <c r="P8" s="1">
-        <v>-8.7</v>
+        <v>-2.3</v>
       </c>
       <c r="Q8" s="2">
         <v>0.0264</v>
@@ -1081,28 +1081,28 @@
         <v>7</v>
       </c>
       <c r="T8" s="2">
-        <v>-0.0079</v>
+        <v>-0.0003</v>
       </c>
       <c r="U8" s="5">
-        <v>3.892</v>
+        <v>3.922</v>
       </c>
       <c r="V8" s="5">
         <v>3.934</v>
       </c>
       <c r="W8" s="2">
-        <v>0.0108</v>
+        <v>0.0031</v>
       </c>
       <c r="X8" s="2">
-        <v>0.0605</v>
+        <v>0.0686</v>
       </c>
       <c r="Y8" s="2">
-        <v>0.192</v>
+        <v>0.2012</v>
       </c>
       <c r="Z8" s="2">
-        <v>0.2756</v>
+        <v>0.2855</v>
       </c>
       <c r="AA8" s="2">
-        <v>0.9383</v>
+        <v>0.9532</v>
       </c>
     </row>
     <row r="9">
@@ -1113,13 +1113,13 @@
         <v>转债ETF</v>
       </c>
       <c r="C9" s="1">
-        <v>19835.2</v>
+        <v>20091.4</v>
       </c>
       <c r="D9" s="1">
-        <v>78.4</v>
+        <v>334.6</v>
       </c>
       <c r="E9" s="2">
-        <v>0.004</v>
+        <v>0.0169</v>
       </c>
       <c r="F9" t="str">
         <v/>
@@ -1134,28 +1134,28 @@
         <v/>
       </c>
       <c r="J9" s="1">
-        <v>-542.44</v>
+        <v>-286.24</v>
       </c>
       <c r="K9" s="2">
-        <v>-0.0266</v>
+        <v>-0.014</v>
       </c>
       <c r="L9" s="1">
-        <v>-542.44</v>
+        <v>-286.24</v>
       </c>
       <c r="M9" s="2">
-        <v>-0.0266</v>
+        <v>-0.014</v>
       </c>
       <c r="N9" s="1">
-        <v>-19.6</v>
+        <v>229.6</v>
       </c>
       <c r="O9" s="1">
-        <v>-534.04</v>
+        <v>-286.24</v>
       </c>
       <c r="P9" s="1">
-        <v>-534.04</v>
+        <v>-286.24</v>
       </c>
       <c r="Q9" s="2">
-        <v>0.6725</v>
+        <v>0.6749</v>
       </c>
       <c r="R9" s="3">
         <v>1400</v>
@@ -1164,28 +1164,28 @@
         <v>7</v>
       </c>
       <c r="T9" s="2">
-        <v>0.004</v>
+        <v>0.0169</v>
       </c>
       <c r="U9" s="5">
-        <v>14.168</v>
+        <v>14.351</v>
       </c>
       <c r="V9" s="5">
         <v>14.555</v>
       </c>
       <c r="W9" s="2">
-        <v>0.0273</v>
+        <v>0.0142</v>
       </c>
       <c r="X9" s="2">
-        <v>-0.0119</v>
+        <v>0.0009</v>
       </c>
       <c r="Y9" s="2">
-        <v>-0.0309</v>
+        <v>-0.0184</v>
       </c>
       <c r="Z9" s="2">
-        <v>0.0415</v>
+        <v>0.055</v>
       </c>
       <c r="AA9" s="2">
-        <v>0.1815</v>
+        <v>0.1967</v>
       </c>
     </row>
     <row r="10">
@@ -1232,13 +1232,13 @@
         <v>2</v>
       </c>
       <c r="O10" s="1">
-        <v>-6.9</v>
+        <v>-6.5</v>
       </c>
       <c r="P10" s="1">
-        <v>-6.9</v>
+        <v>-6.5</v>
       </c>
       <c r="Q10" s="2">
-        <v>0.0226</v>
+        <v>0.0224</v>
       </c>
       <c r="R10" s="3">
         <v>400</v>
@@ -1279,13 +1279,13 @@
         <v>有色ETF</v>
       </c>
       <c r="C11" s="1">
-        <v>856.4</v>
+        <v>854</v>
       </c>
       <c r="D11" s="1">
-        <v>3.6</v>
+        <v>1.2</v>
       </c>
       <c r="E11" s="2">
-        <v>0.0042</v>
+        <v>0.0014</v>
       </c>
       <c r="F11" t="str">
         <v/>
@@ -1300,28 +1300,28 @@
         <v/>
       </c>
       <c r="J11" s="1">
-        <v>-4.1</v>
+        <v>-6.5</v>
       </c>
       <c r="K11" s="2">
-        <v>-0.0048</v>
+        <v>-0.0076</v>
       </c>
       <c r="L11" s="1">
-        <v>-4.1</v>
+        <v>-6.5</v>
       </c>
       <c r="M11" s="2">
-        <v>-0.0048</v>
+        <v>-0.0076</v>
       </c>
       <c r="N11" s="1">
-        <v>-8</v>
+        <v>-10</v>
       </c>
       <c r="O11" s="1">
-        <v>-4.5</v>
+        <v>-6.5</v>
       </c>
       <c r="P11" s="1">
-        <v>-4.5</v>
+        <v>-6.5</v>
       </c>
       <c r="Q11" s="2">
-        <v>0.029</v>
+        <v>0.0287</v>
       </c>
       <c r="R11" s="3">
         <v>400</v>
@@ -1330,28 +1330,28 @@
         <v>7</v>
       </c>
       <c r="T11" s="2">
-        <v>0.0042</v>
+        <v>0.0014</v>
       </c>
       <c r="U11" s="5">
-        <v>2.141</v>
+        <v>2.135</v>
       </c>
       <c r="V11" s="5">
         <v>2.151</v>
       </c>
       <c r="W11" s="2">
-        <v>0.0047</v>
+        <v>0.0075</v>
       </c>
       <c r="X11" s="2">
-        <v>0.0119</v>
+        <v>0.009</v>
       </c>
       <c r="Y11" s="2">
-        <v>0.0434</v>
+        <v>0.0405</v>
       </c>
       <c r="Z11" s="2">
-        <v>0.1974</v>
+        <v>0.1941</v>
       </c>
       <c r="AA11" s="2">
-        <v>0.276</v>
+        <v>0.2724</v>
       </c>
     </row>
     <row r="12">
@@ -1362,13 +1362,13 @@
         <v/>
       </c>
       <c r="C12" s="1">
-        <v>29332.4</v>
+        <v>29604.8</v>
       </c>
       <c r="D12" s="1">
-        <v>85.8</v>
+        <v>358.2</v>
       </c>
       <c r="E12" s="2">
-        <v>0.0029</v>
+        <v>0.0122</v>
       </c>
       <c r="F12" t="str">
         <v/>
@@ -1383,10 +1383,10 @@
         <v/>
       </c>
       <c r="J12" s="1">
-        <v>-659.39</v>
+        <v>-386.99</v>
       </c>
       <c r="K12" s="2">
-        <v>-0.022</v>
+        <v>-0.0129</v>
       </c>
       <c r="L12" t="str">
         <v/>
@@ -1395,13 +1395,13 @@
         <v/>
       </c>
       <c r="N12" s="1">
-        <v>-62.8</v>
+        <v>203.1</v>
       </c>
       <c r="O12" s="1">
-        <v>-650.59</v>
+        <v>-386.99</v>
       </c>
       <c r="P12" s="1">
-        <v>-650.59</v>
+        <v>-386.99</v>
       </c>
       <c r="Q12" s="2">
         <v>0.9945</v>
